--- a/data/XRD/2 Round/Mo_300Sb_35Se.xlsx
+++ b/data/XRD/2 Round/Mo_300Sb_35Se.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/XRD/2 Round/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{9B31F846-1628-488D-A2A2-2740A951091C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAA5C567-7E70-4A94-9714-8A417E2EB269}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{9B31F846-1628-488D-A2A2-2740A951091C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0846095B-58E7-4D96-B220-51781BE33434}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2D3D3D32-E1CC-4904-B78E-5E96BDC77A54}"/>
+    <workbookView xWindow="2880" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{2D3D3D32-E1CC-4904-B78E-5E96BDC77A54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="384">
   <si>
     <t>No.</t>
   </si>
@@ -416,9 +416,6 @@
     <t>272(23)</t>
   </si>
   <si>
-    <t>00-015-0861; 00-022-0733</t>
-  </si>
-  <si>
     <t>2,86</t>
   </si>
   <si>
@@ -923,9 +920,6 @@
     <t>198(13)</t>
   </si>
   <si>
-    <t>00-022-0733</t>
-  </si>
-  <si>
     <t>2,09</t>
   </si>
   <si>
@@ -974,9 +968,6 @@
     <t>91(14)</t>
   </si>
   <si>
-    <t>01-089-1516</t>
-  </si>
-  <si>
     <t>0,96</t>
   </si>
   <si>
@@ -1163,9 +1154,6 @@
     <t>127(10)</t>
   </si>
   <si>
-    <t>00-022-0733; 01-089-1516</t>
-  </si>
-  <si>
     <t>1,34</t>
   </si>
   <si>
@@ -1196,55 +1184,13 @@
     <t>0,157284</t>
   </si>
   <si>
-    <t>00-015-0861; 01-089-1516; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-3009</t>
-  </si>
-  <si>
-    <t>00-015-0861; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 00-022-0733; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-3012</t>
-  </si>
-  <si>
-    <t>96-901-3009; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-3136; 03-065-3952</t>
-  </si>
-  <si>
-    <t>01-083-2437; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 01-083-2437; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 01-085-0567; 03-065-3952</t>
-  </si>
-  <si>
-    <t>00-015-0861; 01-089-1516; 01-085-0567</t>
-  </si>
-  <si>
-    <t>01-085-0567; 01-083-2437</t>
-  </si>
-  <si>
-    <t>96-901-3128</t>
-  </si>
-  <si>
-    <t>01-089-1516; 03-065-3952</t>
-  </si>
-  <si>
-    <t>96-901-3136; 03-065-3952</t>
-  </si>
-  <si>
-    <t>03-065-7442; 01-083-2437</t>
-  </si>
-  <si>
-    <t>96-901-3012</t>
+    <t>00-029-0914</t>
+  </si>
+  <si>
+    <t>00-015-0861; 00-029-0914</t>
+  </si>
+  <si>
+    <t>03-065-7442</t>
   </si>
 </sst>
 </file>
@@ -1297,6 +1243,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1840,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="T4" t="s">
         <v>53</v>
@@ -1896,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="T5" t="s">
         <v>61</v>
@@ -1952,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>385</v>
+        <v>32</v>
       </c>
       <c r="T6" t="s">
         <v>69</v>
@@ -2064,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>294</v>
+        <v>381</v>
       </c>
       <c r="T8" t="s">
         <v>85</v>
@@ -2120,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="T9" t="s">
         <v>93</v>
@@ -2176,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>385</v>
+        <v>32</v>
       </c>
       <c r="T10" t="s">
         <v>101</v>
@@ -2232,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="T11" t="s">
         <v>109</v>
@@ -2344,19 +2294,19 @@
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="T13" t="s">
+        <v>125</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13" t="s">
         <v>126</v>
-      </c>
-      <c r="U13" t="s">
-        <v>45</v>
-      </c>
-      <c r="V13" t="s">
-        <v>35</v>
-      </c>
-      <c r="W13" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2364,34 +2314,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
         <v>128</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
         <v>129</v>
       </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" t="s">
         <v>130</v>
       </c>
-      <c r="M14" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>131</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>132</v>
-      </c>
-      <c r="P14" t="s">
-        <v>133</v>
       </c>
       <c r="Q14" t="s">
         <v>43</v>
@@ -2400,19 +2350,19 @@
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="T14" t="s">
+        <v>133</v>
+      </c>
+      <c r="U14" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" t="s">
         <v>134</v>
-      </c>
-      <c r="U14" t="s">
-        <v>45</v>
-      </c>
-      <c r="V14" t="s">
-        <v>35</v>
-      </c>
-      <c r="W14" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2420,34 +2370,34 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" t="s">
         <v>136</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
         <v>137</v>
       </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" t="s">
         <v>138</v>
       </c>
-      <c r="M15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>139</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>140</v>
-      </c>
-      <c r="P15" t="s">
-        <v>141</v>
       </c>
       <c r="Q15" t="s">
         <v>43</v>
@@ -2456,19 +2406,19 @@
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>389</v>
+        <v>32</v>
       </c>
       <c r="T15" t="s">
+        <v>141</v>
+      </c>
+      <c r="U15" t="s">
+        <v>45</v>
+      </c>
+      <c r="V15" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" t="s">
         <v>142</v>
-      </c>
-      <c r="U15" t="s">
-        <v>45</v>
-      </c>
-      <c r="V15" t="s">
-        <v>35</v>
-      </c>
-      <c r="W15" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2476,34 +2426,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" t="s">
         <v>144</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
         <v>145</v>
       </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" t="s">
         <v>146</v>
       </c>
-      <c r="M16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>147</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>148</v>
-      </c>
-      <c r="P16" t="s">
-        <v>149</v>
       </c>
       <c r="Q16" t="s">
         <v>43</v>
@@ -2512,19 +2462,19 @@
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="T16" t="s">
+        <v>149</v>
+      </c>
+      <c r="U16" t="s">
+        <v>45</v>
+      </c>
+      <c r="V16" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" t="s">
         <v>150</v>
-      </c>
-      <c r="U16" t="s">
-        <v>45</v>
-      </c>
-      <c r="V16" t="s">
-        <v>35</v>
-      </c>
-      <c r="W16" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2532,34 +2482,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" t="s">
         <v>152</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
         <v>153</v>
       </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" t="s">
         <v>154</v>
       </c>
-      <c r="M17" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>155</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>156</v>
-      </c>
-      <c r="P17" t="s">
-        <v>157</v>
       </c>
       <c r="Q17" t="s">
         <v>43</v>
@@ -2568,19 +2518,19 @@
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="T17" t="s">
+        <v>157</v>
+      </c>
+      <c r="U17" t="s">
+        <v>45</v>
+      </c>
+      <c r="V17" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" t="s">
         <v>158</v>
-      </c>
-      <c r="U17" t="s">
-        <v>45</v>
-      </c>
-      <c r="V17" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2588,34 +2538,34 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
         <v>160</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
         <v>161</v>
       </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" t="s">
         <v>162</v>
       </c>
-      <c r="M18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>163</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>164</v>
-      </c>
-      <c r="P18" t="s">
-        <v>165</v>
       </c>
       <c r="Q18" t="s">
         <v>43</v>
@@ -2624,19 +2574,19 @@
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="T18" t="s">
+        <v>165</v>
+      </c>
+      <c r="U18" t="s">
+        <v>45</v>
+      </c>
+      <c r="V18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W18" t="s">
         <v>166</v>
-      </c>
-      <c r="U18" t="s">
-        <v>45</v>
-      </c>
-      <c r="V18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W18" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2644,55 +2594,52 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
         <v>168</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
         <v>169</v>
       </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" t="s">
         <v>170</v>
       </c>
-      <c r="M19" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>171</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>172</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
+        <v>43</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
         <v>173</v>
       </c>
-      <c r="Q19" t="s">
-        <v>43</v>
-      </c>
-      <c r="R19" t="b">
-        <v>1</v>
-      </c>
-      <c r="S19" t="s">
-        <v>390</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
+        <v>45</v>
+      </c>
+      <c r="V19" t="s">
+        <v>35</v>
+      </c>
+      <c r="W19" t="s">
         <v>174</v>
-      </c>
-      <c r="U19" t="s">
-        <v>45</v>
-      </c>
-      <c r="V19" t="s">
-        <v>35</v>
-      </c>
-      <c r="W19" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2700,34 +2647,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" t="s">
         <v>176</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
         <v>177</v>
       </c>
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" t="s">
         <v>178</v>
       </c>
-      <c r="M20" t="s">
-        <v>28</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>179</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>180</v>
-      </c>
-      <c r="P20" t="s">
-        <v>181</v>
       </c>
       <c r="Q20" t="s">
         <v>43</v>
@@ -2736,19 +2683,19 @@
         <v>1</v>
       </c>
       <c r="S20" t="s">
-        <v>385</v>
+        <v>32</v>
       </c>
       <c r="T20" t="s">
+        <v>181</v>
+      </c>
+      <c r="U20" t="s">
+        <v>45</v>
+      </c>
+      <c r="V20" t="s">
+        <v>35</v>
+      </c>
+      <c r="W20" t="s">
         <v>182</v>
-      </c>
-      <c r="U20" t="s">
-        <v>45</v>
-      </c>
-      <c r="V20" t="s">
-        <v>35</v>
-      </c>
-      <c r="W20" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2756,34 +2703,34 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" t="s">
         <v>184</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" t="s">
         <v>185</v>
       </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" t="s">
         <v>186</v>
       </c>
-      <c r="M21" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>187</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>188</v>
-      </c>
-      <c r="P21" t="s">
-        <v>189</v>
       </c>
       <c r="Q21" t="s">
         <v>43</v>
@@ -2792,19 +2739,19 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="T21" t="s">
+        <v>189</v>
+      </c>
+      <c r="U21" t="s">
+        <v>45</v>
+      </c>
+      <c r="V21" t="s">
+        <v>35</v>
+      </c>
+      <c r="W21" t="s">
         <v>190</v>
-      </c>
-      <c r="U21" t="s">
-        <v>45</v>
-      </c>
-      <c r="V21" t="s">
-        <v>35</v>
-      </c>
-      <c r="W21" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2812,34 +2759,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" t="s">
         <v>192</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
         <v>193</v>
       </c>
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" t="s">
         <v>194</v>
       </c>
-      <c r="M22" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>195</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>196</v>
-      </c>
-      <c r="P22" t="s">
-        <v>197</v>
       </c>
       <c r="Q22" t="s">
         <v>43</v>
@@ -2848,19 +2795,19 @@
         <v>1</v>
       </c>
       <c r="S22" t="s">
-        <v>387</v>
+        <v>32</v>
       </c>
       <c r="T22" t="s">
+        <v>197</v>
+      </c>
+      <c r="U22" t="s">
+        <v>45</v>
+      </c>
+      <c r="V22" t="s">
+        <v>35</v>
+      </c>
+      <c r="W22" t="s">
         <v>198</v>
-      </c>
-      <c r="U22" t="s">
-        <v>45</v>
-      </c>
-      <c r="V22" t="s">
-        <v>35</v>
-      </c>
-      <c r="W22" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2868,34 +2815,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" t="s">
         <v>200</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
         <v>201</v>
       </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23" t="s">
         <v>202</v>
       </c>
-      <c r="M23" t="s">
-        <v>28</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>203</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>204</v>
-      </c>
-      <c r="P23" t="s">
-        <v>205</v>
       </c>
       <c r="Q23" t="s">
         <v>43</v>
@@ -2904,19 +2851,19 @@
         <v>1</v>
       </c>
       <c r="S23" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="T23" t="s">
+        <v>205</v>
+      </c>
+      <c r="U23" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" t="s">
+        <v>35</v>
+      </c>
+      <c r="W23" t="s">
         <v>206</v>
-      </c>
-      <c r="U23" t="s">
-        <v>45</v>
-      </c>
-      <c r="V23" t="s">
-        <v>35</v>
-      </c>
-      <c r="W23" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2924,34 +2871,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" t="s">
         <v>208</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" t="s">
         <v>209</v>
       </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" t="s">
         <v>210</v>
       </c>
-      <c r="M24" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>211</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>212</v>
-      </c>
-      <c r="P24" t="s">
-        <v>213</v>
       </c>
       <c r="Q24" t="s">
         <v>43</v>
@@ -2960,19 +2907,19 @@
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>391</v>
+        <v>32</v>
       </c>
       <c r="T24" t="s">
+        <v>213</v>
+      </c>
+      <c r="U24" t="s">
+        <v>45</v>
+      </c>
+      <c r="V24" t="s">
+        <v>35</v>
+      </c>
+      <c r="W24" t="s">
         <v>214</v>
-      </c>
-      <c r="U24" t="s">
-        <v>45</v>
-      </c>
-      <c r="V24" t="s">
-        <v>35</v>
-      </c>
-      <c r="W24" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2980,34 +2927,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" t="s">
         <v>216</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" t="s">
         <v>217</v>
       </c>
-      <c r="D25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
         <v>218</v>
       </c>
-      <c r="M25" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>219</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>220</v>
-      </c>
-      <c r="P25" t="s">
-        <v>221</v>
       </c>
       <c r="Q25" t="s">
         <v>43</v>
@@ -3016,19 +2963,19 @@
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="T25" t="s">
+        <v>221</v>
+      </c>
+      <c r="U25" t="s">
+        <v>45</v>
+      </c>
+      <c r="V25" t="s">
+        <v>35</v>
+      </c>
+      <c r="W25" t="s">
         <v>222</v>
-      </c>
-      <c r="U25" t="s">
-        <v>45</v>
-      </c>
-      <c r="V25" t="s">
-        <v>35</v>
-      </c>
-      <c r="W25" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3036,55 +2983,52 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" t="s">
         <v>224</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
         <v>225</v>
       </c>
-      <c r="D26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" t="s">
         <v>226</v>
       </c>
-      <c r="M26" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>227</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>228</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
+        <v>43</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
         <v>229</v>
       </c>
-      <c r="Q26" t="s">
-        <v>43</v>
-      </c>
-      <c r="R26" t="b">
-        <v>1</v>
-      </c>
-      <c r="S26" t="s">
-        <v>392</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="U26" t="s">
+        <v>45</v>
+      </c>
+      <c r="V26" t="s">
+        <v>35</v>
+      </c>
+      <c r="W26" t="s">
         <v>230</v>
-      </c>
-      <c r="U26" t="s">
-        <v>45</v>
-      </c>
-      <c r="V26" t="s">
-        <v>35</v>
-      </c>
-      <c r="W26" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3092,34 +3036,34 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C27" t="s">
         <v>232</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
         <v>233</v>
       </c>
-      <c r="D27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s">
         <v>234</v>
       </c>
-      <c r="M27" t="s">
-        <v>28</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>235</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>236</v>
-      </c>
-      <c r="P27" t="s">
-        <v>237</v>
       </c>
       <c r="Q27" t="s">
         <v>43</v>
@@ -3131,16 +3075,16 @@
         <v>32</v>
       </c>
       <c r="T27" t="s">
+        <v>237</v>
+      </c>
+      <c r="U27" t="s">
+        <v>45</v>
+      </c>
+      <c r="V27" t="s">
+        <v>35</v>
+      </c>
+      <c r="W27" t="s">
         <v>238</v>
-      </c>
-      <c r="U27" t="s">
-        <v>45</v>
-      </c>
-      <c r="V27" t="s">
-        <v>35</v>
-      </c>
-      <c r="W27" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3148,34 +3092,34 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" t="s">
         <v>240</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" t="s">
         <v>241</v>
       </c>
-      <c r="D28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" t="s">
         <v>242</v>
       </c>
-      <c r="M28" t="s">
-        <v>28</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>243</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>244</v>
-      </c>
-      <c r="P28" t="s">
-        <v>245</v>
       </c>
       <c r="Q28" t="s">
         <v>43</v>
@@ -3187,16 +3131,16 @@
         <v>32</v>
       </c>
       <c r="T28" t="s">
+        <v>245</v>
+      </c>
+      <c r="U28" t="s">
+        <v>45</v>
+      </c>
+      <c r="V28" t="s">
+        <v>35</v>
+      </c>
+      <c r="W28" t="s">
         <v>246</v>
-      </c>
-      <c r="U28" t="s">
-        <v>45</v>
-      </c>
-      <c r="V28" t="s">
-        <v>35</v>
-      </c>
-      <c r="W28" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3204,34 +3148,34 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" t="s">
         <v>248</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" t="s">
         <v>249</v>
       </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" t="s">
         <v>250</v>
       </c>
-      <c r="M29" t="s">
-        <v>28</v>
-      </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>251</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>252</v>
-      </c>
-      <c r="P29" t="s">
-        <v>253</v>
       </c>
       <c r="Q29" t="s">
         <v>43</v>
@@ -3243,16 +3187,16 @@
         <v>32</v>
       </c>
       <c r="T29" t="s">
+        <v>253</v>
+      </c>
+      <c r="U29" t="s">
+        <v>45</v>
+      </c>
+      <c r="V29" t="s">
+        <v>35</v>
+      </c>
+      <c r="W29" t="s">
         <v>254</v>
-      </c>
-      <c r="U29" t="s">
-        <v>45</v>
-      </c>
-      <c r="V29" t="s">
-        <v>35</v>
-      </c>
-      <c r="W29" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3260,34 +3204,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" t="s">
         <v>256</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" t="s">
         <v>257</v>
       </c>
-      <c r="D30" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" t="s">
         <v>258</v>
       </c>
-      <c r="M30" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>259</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>260</v>
-      </c>
-      <c r="P30" t="s">
-        <v>261</v>
       </c>
       <c r="Q30" t="s">
         <v>43</v>
@@ -3296,19 +3240,19 @@
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>393</v>
+        <v>32</v>
       </c>
       <c r="T30" t="s">
+        <v>261</v>
+      </c>
+      <c r="U30" t="s">
+        <v>45</v>
+      </c>
+      <c r="V30" t="s">
+        <v>35</v>
+      </c>
+      <c r="W30" t="s">
         <v>262</v>
-      </c>
-      <c r="U30" t="s">
-        <v>45</v>
-      </c>
-      <c r="V30" t="s">
-        <v>35</v>
-      </c>
-      <c r="W30" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3316,34 +3260,34 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" t="s">
         <v>264</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" t="s">
         <v>265</v>
       </c>
-      <c r="D31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
         <v>266</v>
       </c>
-      <c r="M31" t="s">
-        <v>28</v>
-      </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>267</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>268</v>
-      </c>
-      <c r="P31" t="s">
-        <v>269</v>
       </c>
       <c r="Q31" t="s">
         <v>43</v>
@@ -3352,19 +3296,19 @@
         <v>1</v>
       </c>
       <c r="S31" t="s">
-        <v>394</v>
+        <v>32</v>
       </c>
       <c r="T31" t="s">
+        <v>269</v>
+      </c>
+      <c r="U31" t="s">
+        <v>45</v>
+      </c>
+      <c r="V31" t="s">
+        <v>35</v>
+      </c>
+      <c r="W31" t="s">
         <v>270</v>
-      </c>
-      <c r="U31" t="s">
-        <v>45</v>
-      </c>
-      <c r="V31" t="s">
-        <v>35</v>
-      </c>
-      <c r="W31" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3372,34 +3316,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" t="s">
         <v>272</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" t="s">
         <v>273</v>
       </c>
-      <c r="D32" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" t="s">
         <v>274</v>
       </c>
-      <c r="M32" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>275</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>276</v>
-      </c>
-      <c r="P32" t="s">
-        <v>277</v>
       </c>
       <c r="Q32" t="s">
         <v>43</v>
@@ -3408,19 +3352,19 @@
         <v>1</v>
       </c>
       <c r="S32" t="s">
-        <v>395</v>
+        <v>32</v>
       </c>
       <c r="T32" t="s">
+        <v>277</v>
+      </c>
+      <c r="U32" t="s">
+        <v>45</v>
+      </c>
+      <c r="V32" t="s">
+        <v>35</v>
+      </c>
+      <c r="W32" t="s">
         <v>278</v>
-      </c>
-      <c r="U32" t="s">
-        <v>45</v>
-      </c>
-      <c r="V32" t="s">
-        <v>35</v>
-      </c>
-      <c r="W32" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3428,55 +3372,52 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" t="s">
         <v>280</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" t="s">
         <v>281</v>
       </c>
-      <c r="D33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" t="s">
         <v>282</v>
       </c>
-      <c r="M33" t="s">
-        <v>28</v>
-      </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>283</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>284</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
+        <v>43</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
         <v>285</v>
       </c>
-      <c r="Q33" t="s">
-        <v>43</v>
-      </c>
-      <c r="R33" t="b">
-        <v>1</v>
-      </c>
-      <c r="S33" t="s">
-        <v>396</v>
-      </c>
-      <c r="T33" t="s">
+      <c r="U33" t="s">
+        <v>45</v>
+      </c>
+      <c r="V33" t="s">
+        <v>35</v>
+      </c>
+      <c r="W33" t="s">
         <v>286</v>
-      </c>
-      <c r="U33" t="s">
-        <v>45</v>
-      </c>
-      <c r="V33" t="s">
-        <v>35</v>
-      </c>
-      <c r="W33" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -3484,55 +3425,52 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>287</v>
+      </c>
+      <c r="C34" t="s">
         <v>288</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" t="s">
         <v>289</v>
       </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" t="s">
-        <v>26</v>
-      </c>
-      <c r="K34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" t="s">
         <v>290</v>
       </c>
-      <c r="M34" t="s">
-        <v>28</v>
-      </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>291</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>292</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
+        <v>43</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
         <v>293</v>
       </c>
-      <c r="Q34" t="s">
-        <v>43</v>
-      </c>
-      <c r="R34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="s">
+      <c r="U34" t="s">
+        <v>45</v>
+      </c>
+      <c r="V34" t="s">
+        <v>35</v>
+      </c>
+      <c r="W34" t="s">
         <v>294</v>
-      </c>
-      <c r="T34" t="s">
-        <v>295</v>
-      </c>
-      <c r="U34" t="s">
-        <v>45</v>
-      </c>
-      <c r="V34" t="s">
-        <v>35</v>
-      </c>
-      <c r="W34" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -3540,34 +3478,34 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" t="s">
+        <v>296</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" t="s">
         <v>297</v>
       </c>
-      <c r="C35" t="s">
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" t="s">
         <v>298</v>
       </c>
-      <c r="D35" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" t="s">
-        <v>26</v>
-      </c>
-      <c r="K35" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="O35" t="s">
         <v>299</v>
       </c>
-      <c r="M35" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="P35" t="s">
         <v>300</v>
-      </c>
-      <c r="O35" t="s">
-        <v>301</v>
-      </c>
-      <c r="P35" t="s">
-        <v>302</v>
       </c>
       <c r="Q35" t="s">
         <v>43</v>
@@ -3576,10 +3514,10 @@
         <v>1</v>
       </c>
       <c r="S35" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="T35" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="U35" t="s">
         <v>45</v>
@@ -3588,7 +3526,7 @@
         <v>35</v>
       </c>
       <c r="W35" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -3596,55 +3534,52 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>303</v>
+      </c>
+      <c r="C36" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" t="s">
         <v>305</v>
       </c>
-      <c r="C36" t="s">
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" t="s">
         <v>306</v>
       </c>
-      <c r="D36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" t="s">
-        <v>26</v>
-      </c>
-      <c r="K36" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="O36" t="s">
         <v>307</v>
       </c>
-      <c r="M36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="P36" t="s">
         <v>308</v>
       </c>
-      <c r="O36" t="s">
+      <c r="Q36" t="s">
+        <v>43</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="s">
         <v>309</v>
       </c>
-      <c r="P36" t="s">
+      <c r="U36" t="s">
+        <v>45</v>
+      </c>
+      <c r="V36" t="s">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s">
         <v>310</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>43</v>
-      </c>
-      <c r="R36" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="s">
-        <v>398</v>
-      </c>
-      <c r="T36" t="s">
-        <v>312</v>
-      </c>
-      <c r="U36" t="s">
-        <v>45</v>
-      </c>
-      <c r="V36" t="s">
-        <v>35</v>
-      </c>
-      <c r="W36" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -3652,7 +3587,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C37" t="s">
         <v>72</v>
@@ -3667,40 +3602,37 @@
         <v>26</v>
       </c>
       <c r="L37" t="s">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" t="s">
+        <v>313</v>
+      </c>
+      <c r="O37" t="s">
+        <v>314</v>
+      </c>
+      <c r="P37" t="s">
         <v>315</v>
       </c>
-      <c r="M37" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" t="s">
+      <c r="Q37" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="s">
         <v>316</v>
       </c>
-      <c r="O37" t="s">
+      <c r="U37" t="s">
+        <v>45</v>
+      </c>
+      <c r="V37" t="s">
+        <v>35</v>
+      </c>
+      <c r="W37" t="s">
         <v>317</v>
-      </c>
-      <c r="P37" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>43</v>
-      </c>
-      <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="s">
-        <v>399</v>
-      </c>
-      <c r="T37" t="s">
-        <v>319</v>
-      </c>
-      <c r="U37" t="s">
-        <v>45</v>
-      </c>
-      <c r="V37" t="s">
-        <v>35</v>
-      </c>
-      <c r="W37" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -3708,55 +3640,52 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>318</v>
+      </c>
+      <c r="C38" t="s">
+        <v>319</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" t="s">
+        <v>320</v>
+      </c>
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="s">
         <v>321</v>
       </c>
-      <c r="C38" t="s">
+      <c r="O38" t="s">
         <v>322</v>
       </c>
-      <c r="D38" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" t="s">
-        <v>26</v>
-      </c>
-      <c r="K38" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="P38" t="s">
         <v>323</v>
       </c>
-      <c r="M38" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="Q38" t="s">
+        <v>43</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="s">
         <v>324</v>
       </c>
-      <c r="O38" t="s">
+      <c r="U38" t="s">
+        <v>45</v>
+      </c>
+      <c r="V38" t="s">
+        <v>35</v>
+      </c>
+      <c r="W38" t="s">
         <v>325</v>
-      </c>
-      <c r="P38" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>43</v>
-      </c>
-      <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>398</v>
-      </c>
-      <c r="T38" t="s">
-        <v>327</v>
-      </c>
-      <c r="U38" t="s">
-        <v>45</v>
-      </c>
-      <c r="V38" t="s">
-        <v>35</v>
-      </c>
-      <c r="W38" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -3764,55 +3693,52 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>326</v>
+      </c>
+      <c r="C39" t="s">
+        <v>327</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" t="s">
+        <v>328</v>
+      </c>
+      <c r="M39" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" t="s">
         <v>329</v>
       </c>
-      <c r="C39" t="s">
+      <c r="O39" t="s">
         <v>330</v>
       </c>
-      <c r="D39" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" t="s">
-        <v>26</v>
-      </c>
-      <c r="K39" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="P39" t="s">
         <v>331</v>
       </c>
-      <c r="M39" t="s">
-        <v>28</v>
-      </c>
-      <c r="N39" t="s">
+      <c r="Q39" t="s">
+        <v>43</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
         <v>332</v>
       </c>
-      <c r="O39" t="s">
+      <c r="U39" t="s">
+        <v>45</v>
+      </c>
+      <c r="V39" t="s">
+        <v>35</v>
+      </c>
+      <c r="W39" t="s">
         <v>333</v>
-      </c>
-      <c r="P39" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>43</v>
-      </c>
-      <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="s">
-        <v>398</v>
-      </c>
-      <c r="T39" t="s">
-        <v>335</v>
-      </c>
-      <c r="U39" t="s">
-        <v>45</v>
-      </c>
-      <c r="V39" t="s">
-        <v>35</v>
-      </c>
-      <c r="W39" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -3820,55 +3746,52 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" t="s">
+        <v>335</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" t="s">
+        <v>336</v>
+      </c>
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" t="s">
         <v>337</v>
       </c>
-      <c r="C40" t="s">
+      <c r="O40" t="s">
         <v>338</v>
       </c>
-      <c r="D40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J40" t="s">
-        <v>26</v>
-      </c>
-      <c r="K40" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="P40" t="s">
         <v>339</v>
       </c>
-      <c r="M40" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" t="s">
+      <c r="Q40" t="s">
+        <v>43</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="s">
         <v>340</v>
       </c>
-      <c r="O40" t="s">
+      <c r="U40" t="s">
+        <v>45</v>
+      </c>
+      <c r="V40" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" t="s">
         <v>341</v>
-      </c>
-      <c r="P40" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>43</v>
-      </c>
-      <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="s">
-        <v>390</v>
-      </c>
-      <c r="T40" t="s">
-        <v>343</v>
-      </c>
-      <c r="U40" t="s">
-        <v>45</v>
-      </c>
-      <c r="V40" t="s">
-        <v>35</v>
-      </c>
-      <c r="W40" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -3876,34 +3799,34 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>342</v>
+      </c>
+      <c r="C41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" t="s">
+        <v>344</v>
+      </c>
+      <c r="M41" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" t="s">
         <v>345</v>
       </c>
-      <c r="C41" t="s">
+      <c r="O41" t="s">
         <v>346</v>
       </c>
-      <c r="D41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" t="s">
-        <v>26</v>
-      </c>
-      <c r="K41" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" t="s">
+      <c r="P41" t="s">
         <v>347</v>
-      </c>
-      <c r="M41" t="s">
-        <v>28</v>
-      </c>
-      <c r="N41" t="s">
-        <v>348</v>
-      </c>
-      <c r="O41" t="s">
-        <v>349</v>
-      </c>
-      <c r="P41" t="s">
-        <v>350</v>
       </c>
       <c r="Q41" t="s">
         <v>43</v>
@@ -3912,10 +3835,10 @@
         <v>1</v>
       </c>
       <c r="S41" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="T41" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="U41" t="s">
         <v>45</v>
@@ -3924,7 +3847,7 @@
         <v>35</v>
       </c>
       <c r="W41" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -3932,7 +3855,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C42" t="s">
         <v>120</v>
@@ -3947,40 +3870,37 @@
         <v>26</v>
       </c>
       <c r="L42" t="s">
+        <v>351</v>
+      </c>
+      <c r="M42" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" t="s">
+        <v>352</v>
+      </c>
+      <c r="O42" t="s">
+        <v>353</v>
+      </c>
+      <c r="P42" t="s">
         <v>354</v>
       </c>
-      <c r="M42" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="Q42" t="s">
+        <v>43</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="s">
         <v>355</v>
       </c>
-      <c r="O42" t="s">
+      <c r="U42" t="s">
+        <v>45</v>
+      </c>
+      <c r="V42" t="s">
+        <v>35</v>
+      </c>
+      <c r="W42" t="s">
         <v>356</v>
-      </c>
-      <c r="P42" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>43</v>
-      </c>
-      <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="s">
-        <v>401</v>
-      </c>
-      <c r="T42" t="s">
-        <v>358</v>
-      </c>
-      <c r="U42" t="s">
-        <v>45</v>
-      </c>
-      <c r="V42" t="s">
-        <v>35</v>
-      </c>
-      <c r="W42" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -3988,55 +3908,52 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>357</v>
+      </c>
+      <c r="C43" t="s">
+        <v>358</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" t="s">
+        <v>359</v>
+      </c>
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" t="s">
         <v>360</v>
       </c>
-      <c r="C43" t="s">
+      <c r="O43" t="s">
         <v>361</v>
       </c>
-      <c r="D43" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" t="s">
+      <c r="P43" t="s">
         <v>362</v>
       </c>
-      <c r="M43" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" t="s">
+      <c r="Q43" t="s">
+        <v>43</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="s">
         <v>363</v>
       </c>
-      <c r="O43" t="s">
+      <c r="U43" t="s">
+        <v>45</v>
+      </c>
+      <c r="V43" t="s">
+        <v>35</v>
+      </c>
+      <c r="W43" t="s">
         <v>364</v>
-      </c>
-      <c r="P43" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>43</v>
-      </c>
-      <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="s">
-        <v>294</v>
-      </c>
-      <c r="T43" t="s">
-        <v>366</v>
-      </c>
-      <c r="U43" t="s">
-        <v>45</v>
-      </c>
-      <c r="V43" t="s">
-        <v>35</v>
-      </c>
-      <c r="W43" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -4044,34 +3961,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>365</v>
+      </c>
+      <c r="C44" t="s">
+        <v>366</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44" t="s">
+        <v>367</v>
+      </c>
+      <c r="M44" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" t="s">
         <v>368</v>
       </c>
-      <c r="C44" t="s">
+      <c r="O44" t="s">
         <v>369</v>
       </c>
-      <c r="D44" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" t="s">
-        <v>26</v>
-      </c>
-      <c r="K44" t="s">
-        <v>26</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="P44" t="s">
         <v>370</v>
-      </c>
-      <c r="M44" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" t="s">
-        <v>371</v>
-      </c>
-      <c r="O44" t="s">
-        <v>372</v>
-      </c>
-      <c r="P44" t="s">
-        <v>373</v>
       </c>
       <c r="Q44" t="s">
         <v>43</v>
@@ -4080,10 +3997,10 @@
         <v>1</v>
       </c>
       <c r="S44" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="T44" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U44" t="s">
         <v>45</v>
@@ -4092,7 +4009,7 @@
         <v>35</v>
       </c>
       <c r="W44" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -4100,55 +4017,52 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45" t="s">
+        <v>374</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" t="s">
+        <v>375</v>
+      </c>
+      <c r="M45" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" t="s">
+        <v>376</v>
+      </c>
+      <c r="O45" t="s">
         <v>377</v>
       </c>
-      <c r="C45" t="s">
+      <c r="P45" t="s">
         <v>378</v>
       </c>
-      <c r="D45" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" t="s">
+      <c r="Q45" t="s">
+        <v>43</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
         <v>379</v>
       </c>
-      <c r="M45" t="s">
-        <v>28</v>
-      </c>
-      <c r="N45" t="s">
+      <c r="U45" t="s">
+        <v>45</v>
+      </c>
+      <c r="V45" t="s">
+        <v>35</v>
+      </c>
+      <c r="W45" t="s">
         <v>380</v>
-      </c>
-      <c r="O45" t="s">
-        <v>381</v>
-      </c>
-      <c r="P45" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>43</v>
-      </c>
-      <c r="R45" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="s">
-        <v>311</v>
-      </c>
-      <c r="T45" t="s">
-        <v>383</v>
-      </c>
-      <c r="U45" t="s">
-        <v>45</v>
-      </c>
-      <c r="V45" t="s">
-        <v>35</v>
-      </c>
-      <c r="W45" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
